--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:47</t>
+    <t xml:space="preserve">2026-09-10 00:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:56</t>
+    <t xml:space="preserve">2026-09-18 11:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:05</t>
+    <t xml:space="preserve">2026-09-23 14:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1120,7 +1120,9 @@
       <c r="C34" s="2" t="n">
         <v>8101</v>
       </c>
-      <c r="D34" s="2"/>
+      <c r="D34" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E34" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:26</t>
+    <t xml:space="preserve">2026-10-02 15:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_biobio.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Contulmo</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Chiguayante</t>
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Antuco</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:35</t>
+    <t xml:space="preserve">2026-10-04 10:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:12</t>
+    <t xml:space="preserve">2026-10-05 14:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
